--- a/MEME_OUTPUT/direct_meme_out_2_motif3.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_2_motif3.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.9928</v>
+        <v>0.9926029588164734</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9796</v>
+        <v>0.9794082367053178</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9126</v>
+        <v>0.9124350259896041</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.51359456217513</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.9972</v>
+        <v>0.9970011995201919</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/direct_meme_out_2_motif3.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_2_motif3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TCATC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>TC</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;A&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.9926029588164734</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>CTCATCT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CAT&lt;span style="color: blue; font-weight: bold;"&gt;C&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.9794082367053178</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>GTCGGGT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CGG&lt;span style="color: blue; font-weight: bold;"&gt;G&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9124350259896041</v>
       </c>
     </row>
@@ -564,15 +604,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>TACCTCATCTTTTTTAAGTCGGGTA</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;CCTCATCTTTTTTAAGTCGGG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.51359456217513</v>
       </c>
     </row>
@@ -593,15 +643,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>ATCTTTTTTAAGTCGGGTAT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;CTTTTTTAAGTCGGGT&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9970011995201919</v>
       </c>
     </row>
